--- a/prompt2.xlsx
+++ b/prompt2.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MohitVerma\Desktop\git\translation\SaS-to-python\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4F49239-3678-43AA-9E1C-FEBB18BCDD1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0378977B-8F6F-4C2D-BA7E-51EB75B2A354}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="prompt dictionary" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
   </definedNames>
   <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="17" r:id="rId5"/>
+    <pivotCache cacheId="4" r:id="rId5"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -34,27 +34,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="742" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="291">
   <si>
     <t>Sr.No.</t>
   </si>
   <si>
-    <t>Sheet with data</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
     <t>prompt</t>
   </si>
   <si>
-    <t>NW HYSA</t>
-  </si>
-  <si>
     <t>fetch competitor APY data</t>
-  </si>
-  <si>
-    <t>Ranking of saving products on nerdwallet HYSA page</t>
   </si>
   <si>
     <t xml:space="preserve">Visit the following page 
@@ -72,9 +60,6 @@
 </t>
   </si>
   <si>
-    <t>Ranking of saving products on nerdwallet Standalone page</t>
-  </si>
-  <si>
     <t xml:space="preserve">Visit the following page 
 https://www.nerdwallet.com/m/banking/standout-online-savings-accounts-2
 scrap all the content which is available on the page.
@@ -88,12 +73,6 @@
 Bonus: if any (empty if not available)
 Notes: (minimum balance, eligibility, account type, restrictions — if not stated, empty)
 </t>
-  </si>
-  <si>
-    <t>NW</t>
-  </si>
-  <si>
-    <t>Prompt (nerdwallet, bestmoney, bankrate)--&gt;</t>
   </si>
   <si>
     <t>Visit each of the following links and extract the complete, ordered list of banks or financial institutions and their savings-account offers.
@@ -125,25 +104,13 @@
 Publisher | Rank Order | Bank | Product | APY | Publisher Rating | Bonus | Notes.</t>
   </si>
   <si>
-    <t>BCS review</t>
-  </si>
-  <si>
     <t>Barclays sentiments</t>
   </si>
   <si>
-    <t>top 5 positive and top 5 negtive discussion about barclays on reddit and Doctor of Credit</t>
-  </si>
-  <si>
     <t>Analyze the 2025 Doctor of Credit comments on “Barclays Savings”. Extract the top five positive and top five negative comment themes. Represent each as a hashtag with a short label and an approximate count of occurrences. Present the results in a clean two-section table — one for positives and one for negatives.</t>
   </si>
   <si>
-    <t>DoC + reddit</t>
-  </si>
-  <si>
     <t>top 5 saving products in 2025</t>
-  </si>
-  <si>
-    <t>top 5 saving products in 2025 discussed one reddit and Doctor of Credit</t>
   </si>
   <si>
     <t xml:space="preserve">I want you to run the comparative analysis
@@ -164,13 +131,7 @@
 </t>
   </si>
   <si>
-    <t>saving product ranking</t>
-  </si>
-  <si>
     <t>top 5 monthly saving products in 2025</t>
-  </si>
-  <si>
-    <t>top 5 monthly saving products in 2025 discussed one reddit and Doctor of Credit</t>
   </si>
   <si>
     <t>I want you to run the comparative analysis_x000D_
@@ -730,12 +691,6 @@
   </si>
   <si>
     <t>Given this Python code block, produce a profiling report (cProfile) and optimized version achieving ≥{{x}}% speedup. Explain trade-offs and add tests to ensure parity. Code: {{code}}</t>
-  </si>
-  <si>
-    <t>serial number</t>
-  </si>
-  <si>
-    <t>category</t>
   </si>
   <si>
     <t>Create a customer segmentation campaign brief for retail banking</t>
@@ -1349,6 +1304,29 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1367,12 +1345,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1380,23 +1352,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -7846,7 +7801,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E6D0B8C-D3DB-4D61-81DB-12BC70BC81B9}" name="PivotTable2" cacheId="17" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{7E6D0B8C-D3DB-4D61-81DB-12BC70BC81B9}" name="PivotTable2" cacheId="4" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
   <location ref="J7:AA21" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" numFmtId="164" showAll="0">
@@ -8653,1254 +8608,1118 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G83"/>
+  <dimension ref="B2:E80"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.08984375" customWidth="1"/>
-    <col min="5" max="5" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="7.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="42" customWidth="1"/>
+    <col min="5" max="5" width="7.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="2">
         <v>1</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.35">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="2">
         <v>2</v>
       </c>
-      <c r="C4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>28</v>
+      </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.35">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="2">
         <v>3</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.35">
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="2">
         <v>4</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>6</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="2">
         <v>5</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.35">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="2">
         <v>6</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.35">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="2">
         <v>7</v>
       </c>
-      <c r="C9" s="2"/>
+      <c r="C9" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="D9" s="2" t="s">
-        <v>42</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="2:7" x14ac:dyDescent="0.35">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="2">
         <v>8</v>
       </c>
-      <c r="C10" s="2"/>
+      <c r="C10" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="D10" s="2" t="s">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.35">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="2"/>
+      <c r="C11" s="2" t="s">
+        <v>29</v>
+      </c>
       <c r="D11" s="2" t="s">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="2:7" x14ac:dyDescent="0.35">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="2"/>
+      <c r="C12" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="D12" s="2" t="s">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.35">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="2"/>
+      <c r="C13" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="D13" s="2" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="2">
         <v>12</v>
       </c>
-      <c r="C14" s="2"/>
+      <c r="C14" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="D14" s="2" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="2">
         <v>13</v>
       </c>
-      <c r="C15" s="2"/>
+      <c r="C15" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="D15" s="2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="2">
         <v>14</v>
       </c>
-      <c r="C16" s="2"/>
+      <c r="C16" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="D16" s="2" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2">
         <v>15</v>
       </c>
-      <c r="C17" s="2"/>
+      <c r="C17" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="D17" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="2">
         <v>16</v>
       </c>
-      <c r="C18" s="2"/>
+      <c r="C18" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="D18" s="2" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="2">
         <v>17</v>
       </c>
-      <c r="C19" s="2"/>
+      <c r="C19" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="D19" s="2" t="s">
-        <v>104</v>
+        <v>95</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
         <v>18</v>
       </c>
-      <c r="C20" s="2"/>
+      <c r="C20" s="2" t="s">
+        <v>91</v>
+      </c>
       <c r="D20" s="2" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="2">
         <v>19</v>
       </c>
-      <c r="C21" s="2"/>
+      <c r="C21" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="D21" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
         <v>20</v>
       </c>
-      <c r="C22" s="2"/>
+      <c r="C22" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="D22" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2">
         <v>21</v>
       </c>
-      <c r="C23" s="2"/>
+      <c r="C23" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="D23" s="2" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
         <v>22</v>
       </c>
-      <c r="C24" s="2"/>
+      <c r="C24" s="2" t="s">
+        <v>99</v>
+      </c>
       <c r="D24" s="2" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="2">
         <v>23</v>
       </c>
-      <c r="C25" s="2"/>
+      <c r="C25" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="D25" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.35">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
         <v>24</v>
       </c>
-      <c r="C26" s="2"/>
+      <c r="C26" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="D26" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.35">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="2">
         <v>25</v>
       </c>
-      <c r="C27" s="2"/>
+      <c r="C27" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="D27" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="F27" s="2"/>
-      <c r="G27" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.35">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B28" s="2">
         <v>26</v>
       </c>
-      <c r="C28" s="2"/>
+      <c r="C28" s="2" t="s">
+        <v>108</v>
+      </c>
       <c r="D28" s="2" t="s">
-        <v>121</v>
+        <v>115</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="F28" s="2"/>
-      <c r="G28" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.35">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B29" s="2">
         <v>27</v>
       </c>
-      <c r="C29" s="2"/>
+      <c r="C29" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="D29" s="2" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="F29" s="2"/>
-      <c r="G29" s="2" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.35">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B30" s="2">
         <v>28</v>
       </c>
-      <c r="C30" s="2"/>
+      <c r="C30" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="D30" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F30" s="2"/>
-      <c r="G30" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B31" s="2">
         <v>29</v>
       </c>
-      <c r="C31" s="2"/>
+      <c r="C31" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="D31" s="2" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.35">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B32" s="2">
         <v>30</v>
       </c>
-      <c r="C32" s="2"/>
+      <c r="C32" s="2" t="s">
+        <v>117</v>
+      </c>
       <c r="D32" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B33" s="2">
         <v>31</v>
       </c>
-      <c r="C33" s="2"/>
+      <c r="C33" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="D33" s="2" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="34" spans="2:7" x14ac:dyDescent="0.35">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B34" s="2">
         <v>32</v>
       </c>
-      <c r="C34" s="2"/>
+      <c r="C34" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="D34" s="2" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="35" spans="2:7" x14ac:dyDescent="0.35">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B35" s="2">
         <v>33</v>
       </c>
-      <c r="C35" s="2"/>
+      <c r="C35" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="D35" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F35" s="2"/>
-      <c r="G35" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="36" spans="2:7" x14ac:dyDescent="0.35">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B36" s="2">
         <v>34</v>
       </c>
-      <c r="C36" s="2"/>
+      <c r="C36" s="2" t="s">
+        <v>126</v>
+      </c>
       <c r="D36" s="2" t="s">
-        <v>139</v>
+        <v>133</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F36" s="2"/>
-      <c r="G36" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="37" spans="2:7" x14ac:dyDescent="0.35">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B37" s="2">
         <v>35</v>
       </c>
-      <c r="C37" s="2"/>
+      <c r="C37" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="D37" s="2" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="F37" s="2"/>
-      <c r="G37" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="38" spans="2:7" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B38" s="2">
         <v>36</v>
       </c>
-      <c r="C38" s="2"/>
+      <c r="C38" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="D38" s="2" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F38" s="2"/>
-      <c r="G38" s="2" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="39" spans="2:7" x14ac:dyDescent="0.35">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B39" s="2">
         <v>37</v>
       </c>
-      <c r="C39" s="2"/>
+      <c r="C39" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="D39" s="2" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F39" s="2"/>
-      <c r="G39" s="2" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="40" spans="2:7" x14ac:dyDescent="0.35">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B40" s="2">
         <v>38</v>
       </c>
-      <c r="C40" s="2"/>
+      <c r="C40" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="D40" s="2" t="s">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F40" s="2"/>
-      <c r="G40" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="41" spans="2:7" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B41" s="2">
         <v>39</v>
       </c>
-      <c r="C41" s="2"/>
+      <c r="C41" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="D41" s="2" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F41" s="2"/>
-      <c r="G41" s="2" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="42" spans="2:7" x14ac:dyDescent="0.35">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B42" s="2">
         <v>40</v>
       </c>
-      <c r="C42" s="2"/>
+      <c r="C42" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="D42" s="2" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="F42" s="2"/>
-      <c r="G42" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="43" spans="2:7" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B43" s="2">
         <v>41</v>
       </c>
-      <c r="C43" s="2"/>
+      <c r="C43" s="2" t="s">
+        <v>148</v>
+      </c>
       <c r="D43" s="2" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F43" s="2"/>
-      <c r="G43" s="2" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="44" spans="2:7" x14ac:dyDescent="0.35">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B44" s="2">
         <v>42</v>
       </c>
-      <c r="C44" s="2"/>
+      <c r="C44" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="D44" s="2" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="F44" s="2"/>
-      <c r="G44" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="45" spans="2:7" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B45" s="2">
         <v>43</v>
       </c>
-      <c r="C45" s="2"/>
+      <c r="C45" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="D45" s="2" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F45" s="2"/>
-      <c r="G45" s="2" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="46" spans="2:7" x14ac:dyDescent="0.35">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B46" s="2">
         <v>44</v>
       </c>
-      <c r="C46" s="2"/>
+      <c r="C46" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="D46" s="2" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="F46" s="2"/>
-      <c r="G46" s="2" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="47" spans="2:7" x14ac:dyDescent="0.35">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B47" s="2">
         <v>45</v>
       </c>
-      <c r="C47" s="2"/>
+      <c r="C47" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="D47" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="48" spans="2:7" x14ac:dyDescent="0.35">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B48" s="2">
         <v>46</v>
       </c>
-      <c r="C48" s="2"/>
+      <c r="C48" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="D48" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B49" s="2">
+        <v>47</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B50" s="2">
+        <v>48</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E50" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B51" s="2">
+        <v>49</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B52" s="2">
+        <v>50</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B53" s="2">
+        <v>51</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B54" s="2">
+        <v>52</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B55" s="2">
+        <v>53</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B56" s="2">
+        <v>54</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B57" s="2">
+        <v>55</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F48" s="2"/>
-      <c r="G48" s="2" t="s">
+      <c r="E57" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B58" s="2">
+        <v>56</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="51" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B51" t="s">
+      <c r="E58" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B59" s="2">
+        <v>57</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B60" s="2">
+        <v>58</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B61" s="2">
+        <v>59</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B62" s="2">
+        <v>60</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D62" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C51" t="s">
+      <c r="E62" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B63" s="2">
+        <v>61</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D51" t="s">
-        <v>103</v>
-      </c>
-      <c r="E51" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52" t="s">
-        <v>104</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="E63" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B64" s="2">
+        <v>62</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="E52" t="s">
+      <c r="E64" s="2" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="53" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B53">
-        <v>2</v>
-      </c>
-      <c r="C53" t="s">
-        <v>104</v>
-      </c>
-      <c r="D53" t="s">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B65" s="2">
+        <v>63</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E53" t="s">
+      <c r="E65" s="2" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="54" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B54">
-        <v>3</v>
-      </c>
-      <c r="C54" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" t="s">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B66" s="2">
+        <v>64</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D66" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="E54" t="s">
+      <c r="E66" s="2" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="55" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B55">
-        <v>4</v>
-      </c>
-      <c r="C55" t="s">
-        <v>104</v>
-      </c>
-      <c r="D55" t="s">
+    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B67" s="2">
+        <v>65</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D67" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E55" t="s">
+      <c r="E67" s="2" t="s">
         <v>219</v>
       </c>
     </row>
-    <row r="56" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B56">
-        <v>5</v>
-      </c>
-      <c r="C56" t="s">
-        <v>112</v>
-      </c>
-      <c r="D56" t="s">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B68" s="2">
+        <v>66</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D68" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E56" t="s">
+      <c r="E68" s="2" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="57" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B57">
-        <v>6</v>
-      </c>
-      <c r="C57" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" t="s">
+    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B69" s="2">
+        <v>67</v>
+      </c>
+      <c r="C69" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E57" t="s">
+      <c r="D69" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>221</v>
       </c>
     </row>
-    <row r="58" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B58">
-        <v>7</v>
-      </c>
-      <c r="C58" t="s">
-        <v>112</v>
-      </c>
-      <c r="D58" t="s">
-        <v>187</v>
-      </c>
-      <c r="E58" t="s">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B70" s="2">
+        <v>68</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="59" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B59">
-        <v>8</v>
-      </c>
-      <c r="C59" t="s">
-        <v>112</v>
-      </c>
-      <c r="D59" t="s">
-        <v>188</v>
-      </c>
-      <c r="E59" t="s">
+    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B71" s="2">
+        <v>69</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="60" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B60">
-        <v>9</v>
-      </c>
-      <c r="C60" t="s">
-        <v>121</v>
-      </c>
-      <c r="D60" t="s">
-        <v>189</v>
-      </c>
-      <c r="E60" t="s">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B72" s="2">
+        <v>70</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="61" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B61">
-        <v>10</v>
-      </c>
-      <c r="C61" t="s">
-        <v>121</v>
-      </c>
-      <c r="D61" t="s">
-        <v>190</v>
-      </c>
-      <c r="E61" t="s">
+    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B73" s="2">
+        <v>71</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="62" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B62">
-        <v>11</v>
-      </c>
-      <c r="C62" t="s">
-        <v>121</v>
-      </c>
-      <c r="D62" t="s">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B74" s="2">
+        <v>72</v>
+      </c>
+      <c r="C74" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="E62" t="s">
+      <c r="D74" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="63" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B63">
-        <v>12</v>
-      </c>
-      <c r="C63" t="s">
-        <v>121</v>
-      </c>
-      <c r="D63" t="s">
-        <v>192</v>
-      </c>
-      <c r="E63" t="s">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B75" s="2">
+        <v>73</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="64" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B64">
-        <v>13</v>
-      </c>
-      <c r="C64" t="s">
-        <v>130</v>
-      </c>
-      <c r="D64" t="s">
-        <v>193</v>
-      </c>
-      <c r="E64" t="s">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B76" s="2">
+        <v>74</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>228</v>
       </c>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B65">
-        <v>14</v>
-      </c>
-      <c r="C65" t="s">
-        <v>130</v>
-      </c>
-      <c r="D65" t="s">
-        <v>194</v>
-      </c>
-      <c r="E65" t="s">
+    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B77" s="2">
+        <v>75</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B66">
-        <v>15</v>
-      </c>
-      <c r="C66" t="s">
-        <v>130</v>
-      </c>
-      <c r="D66" t="s">
-        <v>195</v>
-      </c>
-      <c r="E66" t="s">
+    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B78" s="2">
+        <v>76</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>230</v>
       </c>
     </row>
-    <row r="67" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B67">
-        <v>16</v>
-      </c>
-      <c r="C67" t="s">
-        <v>130</v>
-      </c>
-      <c r="D67" t="s">
+    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B79" s="2">
+        <v>77</v>
+      </c>
+      <c r="C79" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E67" t="s">
+      <c r="D79" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B68">
-        <v>17</v>
-      </c>
-      <c r="C68" t="s">
-        <v>139</v>
-      </c>
-      <c r="D68" t="s">
-        <v>197</v>
-      </c>
-      <c r="E68" t="s">
+    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
+      <c r="B80" s="2">
+        <v>78</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B69">
-        <v>18</v>
-      </c>
-      <c r="C69" t="s">
-        <v>139</v>
-      </c>
-      <c r="D69" t="s">
-        <v>198</v>
-      </c>
-      <c r="E69" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B70">
-        <v>19</v>
-      </c>
-      <c r="C70" t="s">
-        <v>139</v>
-      </c>
-      <c r="D70" t="s">
-        <v>199</v>
-      </c>
-      <c r="E70" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="71" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B71">
-        <v>20</v>
-      </c>
-      <c r="C71" t="s">
-        <v>139</v>
-      </c>
-      <c r="D71" t="s">
-        <v>200</v>
-      </c>
-      <c r="E71" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B72">
-        <v>21</v>
-      </c>
-      <c r="C72" t="s">
-        <v>201</v>
-      </c>
-      <c r="D72" t="s">
-        <v>202</v>
-      </c>
-      <c r="E72" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B73">
-        <v>22</v>
-      </c>
-      <c r="C73" t="s">
-        <v>201</v>
-      </c>
-      <c r="D73" t="s">
-        <v>203</v>
-      </c>
-      <c r="E73" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B74">
-        <v>23</v>
-      </c>
-      <c r="C74" t="s">
-        <v>201</v>
-      </c>
-      <c r="D74" t="s">
-        <v>204</v>
-      </c>
-      <c r="E74" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B75">
-        <v>24</v>
-      </c>
-      <c r="C75" t="s">
-        <v>201</v>
-      </c>
-      <c r="D75" t="s">
-        <v>205</v>
-      </c>
-      <c r="E75" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B76">
-        <v>25</v>
-      </c>
-      <c r="C76" t="s">
-        <v>206</v>
-      </c>
-      <c r="D76" t="s">
-        <v>207</v>
-      </c>
-      <c r="E76" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="77" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B77">
-        <v>26</v>
-      </c>
-      <c r="C77" t="s">
-        <v>206</v>
-      </c>
-      <c r="D77" t="s">
-        <v>208</v>
-      </c>
-      <c r="E77" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="78" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B78">
-        <v>27</v>
-      </c>
-      <c r="C78" t="s">
-        <v>206</v>
-      </c>
-      <c r="D78" t="s">
-        <v>209</v>
-      </c>
-      <c r="E78" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="79" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B79">
-        <v>28</v>
-      </c>
-      <c r="C79" t="s">
-        <v>206</v>
-      </c>
-      <c r="D79" t="s">
-        <v>210</v>
-      </c>
-      <c r="E79" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="80" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B80">
-        <v>29</v>
-      </c>
-      <c r="C80" t="s">
-        <v>211</v>
-      </c>
-      <c r="D80" t="s">
-        <v>212</v>
-      </c>
-      <c r="E80" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B81">
-        <v>30</v>
-      </c>
-      <c r="C81" t="s">
-        <v>211</v>
-      </c>
-      <c r="D81" t="s">
-        <v>213</v>
-      </c>
-      <c r="E81" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B82">
-        <v>31</v>
-      </c>
-      <c r="C82" t="s">
-        <v>211</v>
-      </c>
-      <c r="D82" t="s">
-        <v>214</v>
-      </c>
-      <c r="E82" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.35">
-      <c r="B83">
-        <v>32</v>
-      </c>
-      <c r="C83" t="s">
-        <v>211</v>
-      </c>
-      <c r="D83" t="s">
-        <v>215</v>
-      </c>
-      <c r="E83" t="s">
-        <v>247</v>
       </c>
     </row>
   </sheetData>
@@ -9921,326 +9740,326 @@
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B2" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B3" s="3">
         <v>1</v>
       </c>
-      <c r="C3" s="10" t="s">
-        <v>48</v>
+      <c r="C3" s="21" t="s">
+        <v>35</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>50</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B4" s="3">
         <v>2</v>
       </c>
-      <c r="C4" s="11"/>
+      <c r="C4" s="22"/>
       <c r="D4" s="2" t="s">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>52</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B5" s="3">
         <v>3</v>
       </c>
-      <c r="C5" s="11"/>
+      <c r="C5" s="22"/>
       <c r="D5" s="2" t="s">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B6" s="3">
         <v>4</v>
       </c>
-      <c r="C6" s="11"/>
+      <c r="C6" s="22"/>
       <c r="D6" s="2" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B7" s="3">
         <v>5</v>
       </c>
-      <c r="C7" s="12"/>
+      <c r="C7" s="23"/>
       <c r="D7" s="2" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B8" s="3">
         <v>6</v>
       </c>
-      <c r="C8" s="10" t="s">
-        <v>59</v>
+      <c r="C8" s="21" t="s">
+        <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>100</v>
+        <v>87</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B9" s="3">
         <v>7</v>
       </c>
-      <c r="C9" s="11"/>
+      <c r="C9" s="22"/>
       <c r="D9" s="2" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>101</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B10" s="3">
         <v>8</v>
       </c>
-      <c r="C10" s="11"/>
+      <c r="C10" s="22"/>
       <c r="D10" s="2" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>63</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B11" s="2">
         <v>9</v>
       </c>
-      <c r="C11" s="11"/>
+      <c r="C11" s="22"/>
       <c r="D11" s="2" t="s">
-        <v>64</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>65</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B12" s="2">
         <v>10</v>
       </c>
-      <c r="C12" s="12"/>
+      <c r="C12" s="23"/>
       <c r="D12" s="2" t="s">
-        <v>66</v>
+        <v>53</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B13" s="2">
         <v>11</v>
       </c>
-      <c r="C13" s="13" t="s">
-        <v>68</v>
+      <c r="C13" s="24" t="s">
+        <v>55</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>70</v>
+        <v>57</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B14" s="2">
         <v>12</v>
       </c>
-      <c r="C14" s="14"/>
+      <c r="C14" s="25"/>
       <c r="D14" s="2" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B15" s="2">
         <v>13</v>
       </c>
-      <c r="C15" s="14"/>
+      <c r="C15" s="25"/>
       <c r="D15" s="2" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B16" s="2">
         <v>14</v>
       </c>
-      <c r="C16" s="14"/>
+      <c r="C16" s="25"/>
       <c r="D16" s="2" t="s">
-        <v>75</v>
+        <v>62</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B17" s="2">
         <v>15</v>
       </c>
-      <c r="C17" s="15"/>
+      <c r="C17" s="26"/>
       <c r="D17" s="2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>102</v>
+        <v>89</v>
       </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B18" s="2">
         <v>16</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>78</v>
+      <c r="C18" s="24" t="s">
+        <v>65</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B19" s="2">
         <v>17</v>
       </c>
-      <c r="C19" s="14"/>
+      <c r="C19" s="25"/>
       <c r="D19" s="2" t="s">
-        <v>81</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B20" s="2">
         <v>18</v>
       </c>
-      <c r="C20" s="14"/>
+      <c r="C20" s="25"/>
       <c r="D20" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>84</v>
+        <v>71</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B21" s="2">
         <v>19</v>
       </c>
-      <c r="C21" s="14"/>
+      <c r="C21" s="25"/>
       <c r="D21" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>86</v>
+        <v>73</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B22" s="2">
         <v>20</v>
       </c>
-      <c r="C22" s="15"/>
+      <c r="C22" s="26"/>
       <c r="D22" s="2" t="s">
-        <v>87</v>
+        <v>74</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B23" s="2">
         <v>21</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>89</v>
+      <c r="C23" s="24" t="s">
+        <v>76</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B24" s="2">
         <v>22</v>
       </c>
-      <c r="C24" s="14"/>
+      <c r="C24" s="25"/>
       <c r="D24" s="2" t="s">
-        <v>92</v>
+        <v>79</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B25" s="2">
         <v>23</v>
       </c>
-      <c r="C25" s="14"/>
+      <c r="C25" s="25"/>
       <c r="D25" s="2" t="s">
-        <v>94</v>
+        <v>81</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B26" s="2">
         <v>24</v>
       </c>
-      <c r="C26" s="14"/>
+      <c r="C26" s="25"/>
       <c r="D26" s="2" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>97</v>
+        <v>84</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.35">
       <c r="B27" s="2">
         <v>25</v>
       </c>
-      <c r="C27" s="15"/>
+      <c r="C27" s="26"/>
       <c r="D27" s="2" t="s">
-        <v>98</v>
+        <v>85</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -10284,21 +10103,21 @@
   <sheetData>
     <row r="2" spans="3:27" ht="29" x14ac:dyDescent="0.35">
       <c r="C2" s="4" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="3:27" x14ac:dyDescent="0.35">
       <c r="C4" s="6" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
     </row>
     <row r="5" spans="3:27" x14ac:dyDescent="0.35">
@@ -10309,7 +10128,7 @@
         <v>7</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G5" s="8"/>
     </row>
@@ -10321,7 +10140,7 @@
         <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="G6" s="8"/>
     </row>
@@ -10333,14 +10152,14 @@
         <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="G7" s="8"/>
       <c r="J7" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
       <c r="K7" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="8" spans="3:27" x14ac:dyDescent="0.35">
@@ -10351,62 +10170,62 @@
         <v>4</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="G8" s="8"/>
       <c r="J8" t="s">
+        <v>241</v>
+      </c>
+      <c r="K8" t="s">
+        <v>238</v>
+      </c>
+      <c r="L8" t="s">
+        <v>242</v>
+      </c>
+      <c r="M8" t="s">
+        <v>243</v>
+      </c>
+      <c r="N8" t="s">
+        <v>244</v>
+      </c>
+      <c r="O8" t="s">
+        <v>245</v>
+      </c>
+      <c r="P8" t="s">
+        <v>246</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>247</v>
+      </c>
+      <c r="R8" t="s">
+        <v>248</v>
+      </c>
+      <c r="S8" t="s">
+        <v>249</v>
+      </c>
+      <c r="T8" t="s">
+        <v>250</v>
+      </c>
+      <c r="U8" t="s">
+        <v>251</v>
+      </c>
+      <c r="V8" t="s">
+        <v>252</v>
+      </c>
+      <c r="W8" t="s">
+        <v>253</v>
+      </c>
+      <c r="X8" t="s">
+        <v>254</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z8" t="s">
         <v>256</v>
       </c>
-      <c r="K8" t="s">
-        <v>253</v>
-      </c>
-      <c r="L8" t="s">
+      <c r="AA8" t="s">
         <v>257</v>
-      </c>
-      <c r="M8" t="s">
-        <v>258</v>
-      </c>
-      <c r="N8" t="s">
-        <v>259</v>
-      </c>
-      <c r="O8" t="s">
-        <v>260</v>
-      </c>
-      <c r="P8" t="s">
-        <v>261</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>262</v>
-      </c>
-      <c r="R8" t="s">
-        <v>263</v>
-      </c>
-      <c r="S8" t="s">
-        <v>264</v>
-      </c>
-      <c r="T8" t="s">
-        <v>265</v>
-      </c>
-      <c r="U8" t="s">
-        <v>266</v>
-      </c>
-      <c r="V8" t="s">
-        <v>267</v>
-      </c>
-      <c r="W8" t="s">
-        <v>268</v>
-      </c>
-      <c r="X8" t="s">
-        <v>269</v>
-      </c>
-      <c r="Y8" t="s">
-        <v>270</v>
-      </c>
-      <c r="Z8" t="s">
-        <v>271</v>
-      </c>
-      <c r="AA8" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="9" spans="3:27" x14ac:dyDescent="0.35">
@@ -10417,7 +10236,7 @@
         <v>3</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="G9" s="8"/>
       <c r="J9" s="9">
@@ -10477,7 +10296,7 @@
         <v>12</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
       <c r="G10" s="8"/>
       <c r="J10" s="9">
@@ -10537,7 +10356,7 @@
         <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="G11" s="8"/>
       <c r="J11" s="9">
@@ -10603,7 +10422,7 @@
         <v>1</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
       <c r="G12" s="8"/>
       <c r="J12" s="9">
@@ -10666,7 +10485,7 @@
         <v>5</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="G13" s="8"/>
       <c r="J13" s="9">
@@ -10729,7 +10548,7 @@
         <v>2</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="J14" s="9">
         <v>45945</v>
@@ -10791,7 +10610,7 @@
         <v>10</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G15" s="8"/>
       <c r="J15" s="9">
@@ -10851,7 +10670,7 @@
         <v>8</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="G16" s="8"/>
       <c r="J16" s="9">
@@ -10902,7 +10721,7 @@
         <v>13</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="G17" s="8"/>
       <c r="J17" s="9">
@@ -10953,7 +10772,7 @@
         <v>6</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="G18" s="8"/>
       <c r="J18" s="9">
@@ -11001,7 +10820,7 @@
         <v>7</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="J19" s="9">
         <v>45961</v>
@@ -11048,7 +10867,7 @@
         <v>11</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
       <c r="J20" s="9">
         <v>45964</v>
@@ -11098,10 +10917,10 @@
         <v>9</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="J21" s="9" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
       <c r="K21">
         <v>64</v>
@@ -11163,7 +10982,7 @@
         <v>4</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="23" spans="3:27" x14ac:dyDescent="0.35">
@@ -11174,7 +10993,7 @@
         <v>3</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" spans="3:27" x14ac:dyDescent="0.35">
@@ -11185,7 +11004,7 @@
         <v>12</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
     </row>
     <row r="25" spans="3:27" x14ac:dyDescent="0.35">
@@ -11196,7 +11015,7 @@
         <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="26" spans="3:27" x14ac:dyDescent="0.35">
@@ -11207,7 +11026,7 @@
         <v>1</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="27" spans="3:27" x14ac:dyDescent="0.35">
@@ -11218,7 +11037,7 @@
         <v>5</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="3:27" x14ac:dyDescent="0.35">
@@ -11229,7 +11048,7 @@
         <v>2</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="29" spans="3:27" x14ac:dyDescent="0.35">
@@ -11240,7 +11059,7 @@
         <v>10</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" spans="3:27" x14ac:dyDescent="0.35">
@@ -11251,7 +11070,7 @@
         <v>8</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="31" spans="3:27" x14ac:dyDescent="0.35">
@@ -11262,7 +11081,7 @@
         <v>13</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="32" spans="3:27" x14ac:dyDescent="0.35">
@@ -11273,7 +11092,7 @@
         <v>6</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="33" spans="3:5" x14ac:dyDescent="0.35">
@@ -11284,7 +11103,7 @@
         <v>8</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" spans="3:5" x14ac:dyDescent="0.35">
@@ -11295,7 +11114,7 @@
         <v>12</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="35" spans="3:5" x14ac:dyDescent="0.35">
@@ -11306,7 +11125,7 @@
         <v>10</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="36" spans="3:5" x14ac:dyDescent="0.35">
@@ -11317,7 +11136,7 @@
         <v>5</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="37" spans="3:5" x14ac:dyDescent="0.35">
@@ -11328,7 +11147,7 @@
         <v>4</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="38" spans="3:5" x14ac:dyDescent="0.35">
@@ -11339,7 +11158,7 @@
         <v>13</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
     </row>
     <row r="39" spans="3:5" x14ac:dyDescent="0.35">
@@ -11350,7 +11169,7 @@
         <v>16</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.35">
@@ -11361,7 +11180,7 @@
         <v>1</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.35">
@@ -11372,7 +11191,7 @@
         <v>3</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="42" spans="3:5" x14ac:dyDescent="0.35">
@@ -11383,7 +11202,7 @@
         <v>15</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="43" spans="3:5" x14ac:dyDescent="0.35">
@@ -11394,7 +11213,7 @@
         <v>6</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.35">
@@ -11405,7 +11224,7 @@
         <v>2</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.35">
@@ -11416,7 +11235,7 @@
         <v>11</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.35">
@@ -11427,7 +11246,7 @@
         <v>9</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.35">
@@ -11438,7 +11257,7 @@
         <v>14</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.35">
@@ -11449,7 +11268,7 @@
         <v>7</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.35">
@@ -11460,7 +11279,7 @@
         <v>8</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.35">
@@ -11471,7 +11290,7 @@
         <v>12</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="51" spans="3:5" x14ac:dyDescent="0.35">
@@ -11482,7 +11301,7 @@
         <v>10</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.35">
@@ -11493,7 +11312,7 @@
         <v>5</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="53" spans="3:5" x14ac:dyDescent="0.35">
@@ -11504,7 +11323,7 @@
         <v>4</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.35">
@@ -11515,7 +11334,7 @@
         <v>15</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="55" spans="3:5" x14ac:dyDescent="0.35">
@@ -11526,7 +11345,7 @@
         <v>1</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.35">
@@ -11537,7 +11356,7 @@
         <v>3</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="57" spans="3:5" x14ac:dyDescent="0.35">
@@ -11548,7 +11367,7 @@
         <v>14</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="58" spans="3:5" x14ac:dyDescent="0.35">
@@ -11559,7 +11378,7 @@
         <v>6</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="3:5" x14ac:dyDescent="0.35">
@@ -11570,7 +11389,7 @@
         <v>2</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="60" spans="3:5" x14ac:dyDescent="0.35">
@@ -11581,7 +11400,7 @@
         <v>11</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="61" spans="3:5" x14ac:dyDescent="0.35">
@@ -11592,7 +11411,7 @@
         <v>9</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="62" spans="3:5" x14ac:dyDescent="0.35">
@@ -11603,7 +11422,7 @@
         <v>13</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.35">
@@ -11614,7 +11433,7 @@
         <v>7</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.35">
@@ -11625,7 +11444,7 @@
         <v>9</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.35">
@@ -11636,7 +11455,7 @@
         <v>13</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="66" spans="3:5" x14ac:dyDescent="0.35">
@@ -11647,7 +11466,7 @@
         <v>11</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="67" spans="3:5" x14ac:dyDescent="0.35">
@@ -11658,7 +11477,7 @@
         <v>6</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.35">
@@ -11669,7 +11488,7 @@
         <v>5</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="69" spans="3:5" x14ac:dyDescent="0.35">
@@ -11680,7 +11499,7 @@
         <v>15</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="70" spans="3:5" x14ac:dyDescent="0.35">
@@ -11691,7 +11510,7 @@
         <v>1</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="71" spans="3:5" x14ac:dyDescent="0.35">
@@ -11702,7 +11521,7 @@
         <v>4</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="72" spans="3:5" x14ac:dyDescent="0.35">
@@ -11713,7 +11532,7 @@
         <v>3</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="73" spans="3:5" x14ac:dyDescent="0.35">
@@ -11724,7 +11543,7 @@
         <v>7</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" spans="3:5" x14ac:dyDescent="0.35">
@@ -11735,7 +11554,7 @@
         <v>2</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="75" spans="3:5" x14ac:dyDescent="0.35">
@@ -11746,7 +11565,7 @@
         <v>12</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.35">
@@ -11757,7 +11576,7 @@
         <v>10</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.35">
@@ -11768,7 +11587,7 @@
         <v>14</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="78" spans="3:5" x14ac:dyDescent="0.35">
@@ -11779,7 +11598,7 @@
         <v>8</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="79" spans="3:5" x14ac:dyDescent="0.35">
@@ -11790,7 +11609,7 @@
         <v>8</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.35">
@@ -11801,7 +11620,7 @@
         <v>11</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.35">
@@ -11812,7 +11631,7 @@
         <v>10</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.35">
@@ -11823,7 +11642,7 @@
         <v>6</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.35">
@@ -11834,7 +11653,7 @@
         <v>3</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="84" spans="3:5" x14ac:dyDescent="0.35">
@@ -11845,7 +11664,7 @@
         <v>15</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="85" spans="3:5" x14ac:dyDescent="0.35">
@@ -11856,7 +11675,7 @@
         <v>1</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="86" spans="3:5" x14ac:dyDescent="0.35">
@@ -11867,7 +11686,7 @@
         <v>4</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.35">
@@ -11878,7 +11697,7 @@
         <v>13</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.35">
@@ -11889,7 +11708,7 @@
         <v>7</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="89" spans="3:5" x14ac:dyDescent="0.35">
@@ -11900,7 +11719,7 @@
         <v>2</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="90" spans="3:5" x14ac:dyDescent="0.35">
@@ -11911,7 +11730,7 @@
         <v>12</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="91" spans="3:5" x14ac:dyDescent="0.35">
@@ -11922,7 +11741,7 @@
         <v>9</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.35">
@@ -11933,7 +11752,7 @@
         <v>14</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="93" spans="3:5" x14ac:dyDescent="0.35">
@@ -11944,7 +11763,7 @@
         <v>5</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="94" spans="3:5" x14ac:dyDescent="0.35">
@@ -11955,7 +11774,7 @@
         <v>8</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.35">
@@ -11966,7 +11785,7 @@
         <v>11</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="96" spans="3:5" x14ac:dyDescent="0.35">
@@ -11977,7 +11796,7 @@
         <v>10</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="97" spans="3:5" x14ac:dyDescent="0.35">
@@ -11988,7 +11807,7 @@
         <v>6</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="98" spans="3:5" x14ac:dyDescent="0.35">
@@ -11999,7 +11818,7 @@
         <v>3</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="99" spans="3:5" x14ac:dyDescent="0.35">
@@ -12010,7 +11829,7 @@
         <v>14</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="100" spans="3:5" x14ac:dyDescent="0.35">
@@ -12021,7 +11840,7 @@
         <v>1</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="101" spans="3:5" x14ac:dyDescent="0.35">
@@ -12032,7 +11851,7 @@
         <v>4</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="102" spans="3:5" x14ac:dyDescent="0.35">
@@ -12043,7 +11862,7 @@
         <v>7</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="103" spans="3:5" x14ac:dyDescent="0.35">
@@ -12054,7 +11873,7 @@
         <v>2</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="104" spans="3:5" x14ac:dyDescent="0.35">
@@ -12065,7 +11884,7 @@
         <v>12</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="105" spans="3:5" x14ac:dyDescent="0.35">
@@ -12076,7 +11895,7 @@
         <v>9</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="106" spans="3:5" x14ac:dyDescent="0.35">
@@ -12087,7 +11906,7 @@
         <v>13</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="107" spans="3:5" x14ac:dyDescent="0.35">
@@ -12098,7 +11917,7 @@
         <v>5</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
     <row r="108" spans="3:5" x14ac:dyDescent="0.35">
@@ -12109,7 +11928,7 @@
         <v>9</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="109" spans="3:5" x14ac:dyDescent="0.35">
@@ -12120,7 +11939,7 @@
         <v>5</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="110" spans="3:5" x14ac:dyDescent="0.35">
@@ -12131,7 +11950,7 @@
         <v>4</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="111" spans="3:5" x14ac:dyDescent="0.35">
@@ -12142,7 +11961,7 @@
         <v>11</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="112" spans="3:5" x14ac:dyDescent="0.35">
@@ -12153,7 +11972,7 @@
         <v>3</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="113" spans="3:5" x14ac:dyDescent="0.35">
@@ -12164,7 +11983,7 @@
         <v>2</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="114" spans="3:5" x14ac:dyDescent="0.35">
@@ -12175,7 +11994,7 @@
         <v>6</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="3:5" x14ac:dyDescent="0.35">
@@ -12186,7 +12005,7 @@
         <v>1</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="116" spans="3:5" x14ac:dyDescent="0.35">
@@ -12197,7 +12016,7 @@
         <v>7</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="117" spans="3:5" x14ac:dyDescent="0.35">
@@ -12208,7 +12027,7 @@
         <v>8</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="118" spans="3:5" x14ac:dyDescent="0.35">
@@ -12219,7 +12038,7 @@
         <v>10</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="119" spans="3:5" x14ac:dyDescent="0.35">
@@ -12230,7 +12049,7 @@
         <v>9</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="120" spans="3:5" x14ac:dyDescent="0.35">
@@ -12241,7 +12060,7 @@
         <v>5</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="121" spans="3:5" x14ac:dyDescent="0.35">
@@ -12252,7 +12071,7 @@
         <v>4</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="122" spans="3:5" x14ac:dyDescent="0.35">
@@ -12263,7 +12082,7 @@
         <v>11</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="123" spans="3:5" x14ac:dyDescent="0.35">
@@ -12274,7 +12093,7 @@
         <v>3</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="124" spans="3:5" x14ac:dyDescent="0.35">
@@ -12285,7 +12104,7 @@
         <v>2</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="125" spans="3:5" x14ac:dyDescent="0.35">
@@ -12296,7 +12115,7 @@
         <v>6</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="126" spans="3:5" x14ac:dyDescent="0.35">
@@ -12307,7 +12126,7 @@
         <v>1</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="127" spans="3:5" x14ac:dyDescent="0.35">
@@ -12318,7 +12137,7 @@
         <v>7</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="128" spans="3:5" x14ac:dyDescent="0.35">
@@ -12329,7 +12148,7 @@
         <v>8</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="129" spans="3:5" x14ac:dyDescent="0.35">
@@ -12340,7 +12159,7 @@
         <v>10</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="130" spans="3:5" x14ac:dyDescent="0.35">
@@ -12351,7 +12170,7 @@
         <v>8</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="131" spans="3:5" x14ac:dyDescent="0.35">
@@ -12362,7 +12181,7 @@
         <v>4</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="132" spans="3:5" x14ac:dyDescent="0.35">
@@ -12373,7 +12192,7 @@
         <v>3</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="133" spans="3:5" x14ac:dyDescent="0.35">
@@ -12384,7 +12203,7 @@
         <v>10</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="134" spans="3:5" x14ac:dyDescent="0.35">
@@ -12395,7 +12214,7 @@
         <v>2</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="135" spans="3:5" x14ac:dyDescent="0.35">
@@ -12406,7 +12225,7 @@
         <v>5</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="136" spans="3:5" x14ac:dyDescent="0.35">
@@ -12417,7 +12236,7 @@
         <v>1</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="137" spans="3:5" x14ac:dyDescent="0.35">
@@ -12428,7 +12247,7 @@
         <v>6</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="138" spans="3:5" x14ac:dyDescent="0.35">
@@ -12439,7 +12258,7 @@
         <v>7</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="139" spans="3:5" x14ac:dyDescent="0.35">
@@ -12450,7 +12269,7 @@
         <v>9</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="140" spans="3:5" x14ac:dyDescent="0.35">
@@ -12461,7 +12280,7 @@
         <v>7</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="141" spans="3:5" x14ac:dyDescent="0.35">
@@ -12472,7 +12291,7 @@
         <v>4</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="142" spans="3:5" x14ac:dyDescent="0.35">
@@ -12483,7 +12302,7 @@
         <v>3</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="143" spans="3:5" x14ac:dyDescent="0.35">
@@ -12494,7 +12313,7 @@
         <v>10</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="144" spans="3:5" x14ac:dyDescent="0.35">
@@ -12505,7 +12324,7 @@
         <v>2</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="145" spans="3:5" x14ac:dyDescent="0.35">
@@ -12516,7 +12335,7 @@
         <v>5</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="146" spans="3:5" x14ac:dyDescent="0.35">
@@ -12527,7 +12346,7 @@
         <v>1</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="147" spans="3:5" x14ac:dyDescent="0.35">
@@ -12538,7 +12357,7 @@
         <v>8</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="148" spans="3:5" x14ac:dyDescent="0.35">
@@ -12549,7 +12368,7 @@
         <v>6</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="149" spans="3:5" x14ac:dyDescent="0.35">
@@ -12560,7 +12379,7 @@
         <v>9</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="150" spans="3:5" x14ac:dyDescent="0.35">
@@ -12571,7 +12390,7 @@
         <v>9</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="3:5" x14ac:dyDescent="0.35">
@@ -12582,7 +12401,7 @@
         <v>7</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="152" spans="3:5" x14ac:dyDescent="0.35">
@@ -12593,7 +12412,7 @@
         <v>4</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="153" spans="3:5" x14ac:dyDescent="0.35">
@@ -12604,7 +12423,7 @@
         <v>3</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="154" spans="3:5" x14ac:dyDescent="0.35">
@@ -12615,7 +12434,7 @@
         <v>11</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="155" spans="3:5" x14ac:dyDescent="0.35">
@@ -12626,7 +12445,7 @@
         <v>2</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="156" spans="3:5" x14ac:dyDescent="0.35">
@@ -12637,7 +12456,7 @@
         <v>5</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="157" spans="3:5" x14ac:dyDescent="0.35">
@@ -12648,7 +12467,7 @@
         <v>1</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="158" spans="3:5" x14ac:dyDescent="0.35">
@@ -12659,7 +12478,7 @@
         <v>8</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="159" spans="3:5" x14ac:dyDescent="0.35">
@@ -12670,7 +12489,7 @@
         <v>6</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="160" spans="3:5" x14ac:dyDescent="0.35">
@@ -12681,7 +12500,7 @@
         <v>10</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="161" spans="3:5" x14ac:dyDescent="0.35">
@@ -12692,7 +12511,7 @@
         <v>8</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="162" spans="3:5" x14ac:dyDescent="0.35">
@@ -12703,7 +12522,7 @@
         <v>10</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="163" spans="3:5" x14ac:dyDescent="0.35">
@@ -12714,7 +12533,7 @@
         <v>5</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="164" spans="3:5" x14ac:dyDescent="0.35">
@@ -12725,7 +12544,7 @@
         <v>4</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="165" spans="3:5" x14ac:dyDescent="0.35">
@@ -12736,7 +12555,7 @@
         <v>13</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
     <row r="166" spans="3:5" x14ac:dyDescent="0.35">
@@ -12747,7 +12566,7 @@
         <v>3</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="167" spans="3:5" x14ac:dyDescent="0.35">
@@ -12758,7 +12577,7 @@
         <v>2</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="168" spans="3:5" x14ac:dyDescent="0.35">
@@ -12769,7 +12588,7 @@
         <v>6</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="169" spans="3:5" x14ac:dyDescent="0.35">
@@ -12780,7 +12599,7 @@
         <v>1</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="170" spans="3:5" x14ac:dyDescent="0.35">
@@ -12791,7 +12610,7 @@
         <v>11</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="171" spans="3:5" x14ac:dyDescent="0.35">
@@ -12802,7 +12621,7 @@
         <v>9</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="172" spans="3:5" x14ac:dyDescent="0.35">
@@ -12813,7 +12632,7 @@
         <v>12</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="173" spans="3:5" x14ac:dyDescent="0.35">
@@ -12824,7 +12643,7 @@
         <v>7</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
     </row>
   </sheetData>
@@ -12855,344 +12674,344 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B2" s="16">
+      <c r="B2" s="10">
         <v>45966</v>
       </c>
     </row>
     <row r="4" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B4" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="F4" s="19" t="s">
-        <v>274</v>
+      <c r="B4" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C4" s="12"/>
+      <c r="D4" s="12"/>
+      <c r="F4" s="13" t="s">
+        <v>259</v>
       </c>
       <c r="G4" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B6" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="G6" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
+      <c r="B6" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="G6" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B7" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="C7" s="21"/>
-      <c r="D7" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E7" s="21"/>
-      <c r="G7" s="22" t="s">
-        <v>279</v>
-      </c>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22" t="s">
-        <v>280</v>
-      </c>
-      <c r="J7" s="22"/>
+      <c r="B7" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="E7" s="28"/>
+      <c r="G7" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="H7" s="29"/>
+      <c r="I7" s="29" t="s">
+        <v>265</v>
+      </c>
+      <c r="J7" s="29"/>
     </row>
     <row r="8" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B8" s="23" t="s">
+      <c r="B8" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B9" s="17">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="C8" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="D8" s="23" t="s">
+      <c r="D9" s="17">
+        <v>1</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="E8" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="F8" s="25"/>
-      <c r="G8" s="23" t="s">
+      <c r="G9" s="17">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="H8" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="I8" s="23" t="s">
+      <c r="I9" s="17">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="J8" s="24" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B9" s="26">
-        <v>1</v>
-      </c>
-      <c r="C9" s="2" t="s">
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B10" s="17">
+        <v>2</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D10" s="17">
+        <v>2</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="G10" s="17">
+        <v>2</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="I10" s="17">
+        <v>2</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B11" s="17">
+        <v>3</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="D11" s="17">
+        <v>3</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="G11" s="17">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="I11" s="17">
+        <v>3</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B12" s="17">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="17">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="G12" s="17">
+        <v>4</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="I12" s="17">
+        <v>4</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B13" s="17">
+        <v>5</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="D13" s="17">
+        <v>5</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="G13" s="17">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="I13" s="17"/>
+      <c r="J13" s="2"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B14" s="17">
+        <v>6</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D14" s="17">
+        <v>6</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="G14" s="17">
+        <v>6</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="I14" s="17"/>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B15" s="17">
+        <v>7</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D15" s="17">
+        <v>7</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="G15" s="17">
+        <v>7</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="I15" s="17"/>
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B16" s="17">
+        <v>8</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" s="17">
+        <v>8</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="G16" s="17">
+        <v>8</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="I16" s="17"/>
+      <c r="J16" s="2"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B19" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="20"/>
+      <c r="F19" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="G19" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B21" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C21" s="27"/>
+      <c r="D21" s="27"/>
+      <c r="E21" s="27"/>
+      <c r="G21" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="H21" s="27"/>
+      <c r="I21" s="27"/>
+      <c r="J21" s="27"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B22" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="C22" s="28"/>
+      <c r="D22" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" s="28"/>
+      <c r="G22" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="H22" s="28"/>
+      <c r="I22" s="28" t="s">
+        <v>265</v>
+      </c>
+      <c r="J22" s="28"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B23" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="D9" s="26">
-        <v>1</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="D23" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="E23" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="G9" s="26">
-        <v>1</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="G23" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="H23" s="15" t="s">
         <v>266</v>
       </c>
-      <c r="I9" s="26">
-        <v>1</v>
-      </c>
-      <c r="J9" s="2" t="s">
+      <c r="I23" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="J23" s="15" t="s">
         <v>266</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B10" s="26">
-        <v>2</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="D10" s="26">
-        <v>2</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="G10" s="26">
-        <v>2</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="I10" s="26">
-        <v>2</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B11" s="26">
-        <v>3</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="D11" s="26">
-        <v>3</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G11" s="26">
-        <v>3</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="I11" s="26">
-        <v>3</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B12" s="26">
-        <v>4</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="D12" s="26">
-        <v>4</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="G12" s="26">
-        <v>4</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="I12" s="26">
-        <v>4</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B13" s="26">
-        <v>5</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D13" s="26">
-        <v>5</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="G13" s="26">
-        <v>5</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="I13" s="26"/>
-      <c r="J13" s="2"/>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B14" s="26">
-        <v>6</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="D14" s="26">
-        <v>6</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="G14" s="26">
-        <v>6</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="I14" s="26"/>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B15" s="26">
-        <v>7</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="D15" s="26">
-        <v>7</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="G15" s="26">
-        <v>7</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I15" s="26"/>
-      <c r="J15" s="2"/>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B16" s="26">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="D16" s="26">
-        <v>8</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G16" s="26">
-        <v>8</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="I16" s="26"/>
-      <c r="J16" s="2"/>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B19" s="27" t="s">
-        <v>282</v>
-      </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="29"/>
-      <c r="F19" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="G19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B21" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C21" s="20"/>
-      <c r="D21" s="20"/>
-      <c r="E21" s="20"/>
-      <c r="G21" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
-      <c r="J21" s="20"/>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B22" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E22" s="21"/>
-      <c r="G22" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="J22" s="21"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B23" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="C23" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="D23" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="E23" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="G23" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="H23" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="I23" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="J23" s="24" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="24" spans="2:10" x14ac:dyDescent="0.35">
@@ -13200,25 +13019,25 @@
         <v>1</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D24" s="2">
         <v>1</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="I24" s="2">
         <v>1</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.35">
@@ -13226,25 +13045,25 @@
         <v>2</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="D25" s="2">
         <v>2</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="G25" s="2">
         <v>2</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="I25" s="2">
         <v>2</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="26" spans="2:10" x14ac:dyDescent="0.35">
@@ -13252,25 +13071,25 @@
         <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="D26" s="2">
         <v>3</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="G26" s="2">
         <v>3</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="I26" s="2">
         <v>3</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.35">
@@ -13278,25 +13097,25 @@
         <v>4</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="D27" s="2">
         <v>4</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="G27" s="2">
         <v>4</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="I27" s="2">
         <v>4</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.35">
@@ -13304,25 +13123,25 @@
         <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D28" s="2">
         <v>5</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="G28" s="2">
         <v>5</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="I28" s="2">
         <v>5</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
     </row>
     <row r="29" spans="2:10" x14ac:dyDescent="0.35">
@@ -13330,25 +13149,25 @@
         <v>6</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="D29" s="2">
         <v>6</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="G29" s="2">
         <v>6</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="I29" s="2">
         <v>6</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" spans="2:10" x14ac:dyDescent="0.35">
@@ -13356,25 +13175,25 @@
         <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D30" s="2">
         <v>7</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G30" s="2">
         <v>7</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="I30" s="2">
         <v>7</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" spans="2:10" x14ac:dyDescent="0.35">
@@ -13382,25 +13201,25 @@
         <v>8</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="D31" s="2">
         <v>8</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="G31" s="2">
         <v>8</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="I31" s="2">
         <v>8</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
     </row>
     <row r="32" spans="2:10" x14ac:dyDescent="0.35">
@@ -13408,25 +13227,25 @@
         <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="D32" s="2">
         <v>9</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="G32" s="2">
         <v>9</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="I32" s="2">
         <v>9</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
     </row>
     <row r="33" spans="2:10" x14ac:dyDescent="0.35">
@@ -13434,25 +13253,25 @@
         <v>10</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="D33" s="2">
         <v>10</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G33" s="2">
         <v>10</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="I33" s="2">
         <v>10</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.35">
@@ -13460,25 +13279,25 @@
         <v>11</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D34" s="2">
         <v>11</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="G34" s="2">
         <v>11</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="I34" s="2">
         <v>11</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
     </row>
     <row r="35" spans="2:10" x14ac:dyDescent="0.35">
@@ -13486,25 +13305,25 @@
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D35" s="2">
         <v>12</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="G35" s="2">
         <v>12</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="I35" s="2">
         <v>12</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
     </row>
     <row r="36" spans="2:10" x14ac:dyDescent="0.35">
@@ -13512,25 +13331,25 @@
         <v>13</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="D36" s="2">
         <v>13</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="G36" s="2">
         <v>13</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="I36" s="2">
         <v>13</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
     </row>
     <row r="37" spans="2:10" x14ac:dyDescent="0.35">
@@ -13538,7 +13357,7 @@
         <v>14</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="38" spans="2:10" x14ac:dyDescent="0.35">
@@ -13546,7 +13365,7 @@
         <v>15</v>
       </c>
       <c r="J38" s="2" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
     </row>
     <row r="39" spans="2:10" x14ac:dyDescent="0.35">
@@ -13554,7 +13373,7 @@
         <v>16</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="40" spans="2:10" x14ac:dyDescent="0.35">
@@ -13562,7 +13381,7 @@
         <v>17</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="41" spans="2:10" x14ac:dyDescent="0.35">
@@ -13570,7 +13389,7 @@
         <v>18</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" spans="2:10" x14ac:dyDescent="0.35">
@@ -13578,7 +13397,7 @@
         <v>19</v>
       </c>
       <c r="J42" s="2" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
     </row>
     <row r="43" spans="2:10" x14ac:dyDescent="0.35">
@@ -13586,7 +13405,7 @@
         <v>20</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
     </row>
     <row r="44" spans="2:10" x14ac:dyDescent="0.35">
@@ -13594,7 +13413,7 @@
         <v>21</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="45" spans="2:10" x14ac:dyDescent="0.35">
@@ -13602,7 +13421,7 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
     </row>
     <row r="46" spans="2:10" x14ac:dyDescent="0.35">
@@ -13610,7 +13429,7 @@
         <v>23</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
     </row>
     <row r="47" spans="2:10" x14ac:dyDescent="0.35">
@@ -13618,7 +13437,7 @@
         <v>24</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="48" spans="2:10" x14ac:dyDescent="0.35">
@@ -13626,57 +13445,57 @@
         <v>25</v>
       </c>
       <c r="J48" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B49" s="10">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="B51" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="F51" s="13" t="s">
         <v>268</v>
       </c>
-    </row>
-    <row r="49" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B49" s="16">
-        <v>45968</v>
-      </c>
-    </row>
-    <row r="51" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B51" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="F51" s="19" t="s">
-        <v>283</v>
-      </c>
       <c r="G51" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
     </row>
     <row r="54" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B54" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C54" s="20"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
+      <c r="B54" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
     </row>
     <row r="55" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B55" s="21" t="s">
-        <v>278</v>
-      </c>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E55" s="21"/>
+      <c r="B55" s="28" t="s">
+        <v>263</v>
+      </c>
+      <c r="C55" s="28"/>
+      <c r="D55" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="E55" s="28"/>
     </row>
     <row r="56" spans="2:7" x14ac:dyDescent="0.35">
-      <c r="B56" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="C56" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="D56" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="E56" s="24" t="s">
-        <v>281</v>
+      <c r="B56" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="E56" s="15" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.35">
@@ -13684,13 +13503,13 @@
         <v>1</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="D57" s="2">
         <v>1</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.35">
@@ -13698,13 +13517,13 @@
         <v>2</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="D58" s="2">
         <v>2</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="59" spans="2:7" x14ac:dyDescent="0.35">
@@ -13712,13 +13531,13 @@
         <v>3</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
       <c r="D59" s="2">
         <v>3</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
     </row>
     <row r="60" spans="2:7" x14ac:dyDescent="0.35">
@@ -13726,13 +13545,13 @@
         <v>4</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D60" s="2">
         <v>4</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.35">
@@ -13740,13 +13559,13 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D61" s="2">
         <v>5</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" spans="2:7" x14ac:dyDescent="0.35">
@@ -13754,13 +13573,13 @@
         <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="D62" s="2">
         <v>6</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.35">
@@ -13768,13 +13587,13 @@
         <v>7</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="D63" s="2">
         <v>7</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="64" spans="2:7" x14ac:dyDescent="0.35">
@@ -13782,90 +13601,90 @@
         <v>8</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D64" s="2">
         <v>8</v>
       </c>
       <c r="E64" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B66" s="10">
+        <v>45968</v>
+      </c>
+    </row>
+    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B68" s="18" t="s">
+        <v>267</v>
+      </c>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="20"/>
+      <c r="F68" s="13" t="s">
+        <v>268</v>
+      </c>
+      <c r="G68" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B70" s="27" t="s">
+        <v>261</v>
+      </c>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="G70" s="27" t="s">
+        <v>262</v>
+      </c>
+      <c r="H70" s="27"/>
+      <c r="I70" s="27"/>
+      <c r="J70" s="27"/>
+    </row>
+    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="B71" s="28" t="s">
+        <v>270</v>
+      </c>
+      <c r="C71" s="28"/>
+      <c r="D71" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="E71" s="28"/>
+      <c r="G71" s="28" t="s">
+        <v>264</v>
+      </c>
+      <c r="H71" s="28"/>
+      <c r="I71" s="28" t="s">
         <v>265</v>
       </c>
-    </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B66" s="16">
-        <v>45968</v>
-      </c>
-    </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B68" s="27" t="s">
-        <v>282</v>
-      </c>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="29"/>
-      <c r="F68" s="19" t="s">
-        <v>283</v>
-      </c>
-      <c r="G68" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B70" s="20" t="s">
-        <v>276</v>
-      </c>
-      <c r="C70" s="20"/>
-      <c r="D70" s="20"/>
-      <c r="E70" s="20"/>
-      <c r="G70" s="20" t="s">
-        <v>277</v>
-      </c>
-      <c r="H70" s="20"/>
-      <c r="I70" s="20"/>
-      <c r="J70" s="20"/>
-    </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B71" s="21" t="s">
-        <v>285</v>
-      </c>
-      <c r="C71" s="21"/>
-      <c r="D71" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="E71" s="21"/>
-      <c r="G71" s="21" t="s">
-        <v>279</v>
-      </c>
-      <c r="H71" s="21"/>
-      <c r="I71" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="J71" s="21"/>
+      <c r="J71" s="28"/>
     </row>
     <row r="72" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B72" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="C72" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="D72" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="E72" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="G72" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="H72" s="24" t="s">
-        <v>281</v>
-      </c>
-      <c r="I72" s="24" t="s">
-        <v>251</v>
-      </c>
-      <c r="J72" s="24" t="s">
-        <v>281</v>
+      <c r="B72" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C72" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="D72" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="E72" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>266</v>
+      </c>
+      <c r="I72" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="J72" s="15" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="73" spans="2:10" x14ac:dyDescent="0.35">
@@ -13873,25 +13692,25 @@
         <v>1</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="D73" s="2">
         <v>1</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="G73" s="2">
         <v>1</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="I73" s="2">
         <v>1</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
     </row>
     <row r="74" spans="2:10" x14ac:dyDescent="0.35">
@@ -13899,25 +13718,25 @@
         <v>2</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="D74" s="2">
         <v>2</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="G74" s="2">
         <v>2</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="I74" s="2">
         <v>2</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="75" spans="2:10" x14ac:dyDescent="0.35">
@@ -13925,25 +13744,25 @@
         <v>3</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="D75" s="2">
         <v>3</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="G75" s="2">
         <v>3</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="I75" s="2">
         <v>3</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="76" spans="2:10" x14ac:dyDescent="0.35">
@@ -13951,25 +13770,25 @@
         <v>4</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="D76" s="2">
         <v>4</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="G76" s="2">
         <v>4</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
       <c r="I76" s="2">
         <v>4</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
     </row>
     <row r="77" spans="2:10" x14ac:dyDescent="0.35">
@@ -13977,25 +13796,25 @@
         <v>5</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="D77" s="2">
         <v>5</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="G77" s="2">
         <v>5</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
       <c r="I77" s="2">
         <v>5</v>
       </c>
       <c r="J77" s="2" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
     </row>
     <row r="78" spans="2:10" x14ac:dyDescent="0.35">
@@ -14003,25 +13822,25 @@
         <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="D78" s="2">
         <v>6</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="G78" s="2">
         <v>6</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
       <c r="I78" s="2">
         <v>6</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
     </row>
     <row r="79" spans="2:10" x14ac:dyDescent="0.35">
@@ -14029,25 +13848,25 @@
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D79" s="2">
         <v>7</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="G79" s="2">
         <v>7</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="I79" s="2">
         <v>7</v>
       </c>
       <c r="J79" s="2" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
     </row>
     <row r="80" spans="2:10" x14ac:dyDescent="0.35">
@@ -14055,25 +13874,25 @@
         <v>8</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="D80" s="2">
         <v>8</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="G80" s="2">
         <v>8</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="I80" s="2">
         <v>8</v>
       </c>
       <c r="J80" s="2" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
     </row>
     <row r="81" spans="2:10" x14ac:dyDescent="0.35">
@@ -14081,25 +13900,25 @@
         <v>9</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="D81" s="2">
         <v>9</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="G81" s="2">
         <v>9</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="I81" s="2">
         <v>9</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
     </row>
     <row r="82" spans="2:10" x14ac:dyDescent="0.35">
@@ -14107,25 +13926,25 @@
         <v>10</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="D82" s="2">
         <v>10</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="G82" s="2">
         <v>10</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
       <c r="I82" s="2">
         <v>10</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
     </row>
     <row r="83" spans="2:10" x14ac:dyDescent="0.35">
@@ -14133,25 +13952,25 @@
         <v>11</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="D83" s="2">
         <v>11</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="G83" s="2">
         <v>11</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="I83" s="2">
         <v>11</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
     </row>
     <row r="84" spans="2:10" x14ac:dyDescent="0.35">
@@ -14159,25 +13978,25 @@
         <v>12</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="D84" s="2">
         <v>12</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="G84" s="2">
         <v>12</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="I84" s="2">
         <v>12</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
     </row>
     <row r="85" spans="2:10" x14ac:dyDescent="0.35">
@@ -14185,25 +14004,25 @@
         <v>13</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="D85" s="2">
         <v>13</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="G85" s="2">
         <v>13</v>
       </c>
       <c r="H85" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="I85" s="2">
         <v>13</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
     </row>
     <row r="86" spans="2:10" x14ac:dyDescent="0.35">
@@ -14211,7 +14030,7 @@
         <v>14</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="87" spans="2:10" x14ac:dyDescent="0.35">
@@ -14219,7 +14038,7 @@
         <v>15</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
     </row>
     <row r="88" spans="2:10" x14ac:dyDescent="0.35">
@@ -14227,7 +14046,7 @@
         <v>16</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
     </row>
     <row r="89" spans="2:10" x14ac:dyDescent="0.35">
@@ -14235,7 +14054,7 @@
         <v>17</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="90" spans="2:10" x14ac:dyDescent="0.35">
@@ -14243,7 +14062,7 @@
         <v>18</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="91" spans="2:10" x14ac:dyDescent="0.35">
@@ -14251,7 +14070,7 @@
         <v>19</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
     </row>
     <row r="92" spans="2:10" x14ac:dyDescent="0.35">
@@ -14259,7 +14078,7 @@
         <v>20</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
     </row>
     <row r="93" spans="2:10" x14ac:dyDescent="0.35">
@@ -14267,7 +14086,7 @@
         <v>21</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
     </row>
     <row r="94" spans="2:10" x14ac:dyDescent="0.35">
@@ -14275,7 +14094,7 @@
         <v>22</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
     </row>
     <row r="95" spans="2:10" x14ac:dyDescent="0.35">
@@ -14283,7 +14102,7 @@
         <v>23</v>
       </c>
       <c r="J95" s="2" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
     </row>
     <row r="96" spans="2:10" x14ac:dyDescent="0.35">
@@ -14291,7 +14110,7 @@
         <v>24</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
     </row>
     <row r="97" spans="9:10" x14ac:dyDescent="0.35">
@@ -14299,16 +14118,17 @@
         <v>25</v>
       </c>
       <c r="J97" s="2" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="21">
-    <mergeCell ref="B54:E54"/>
-    <mergeCell ref="B55:C55"/>
-    <mergeCell ref="D55:E55"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="G70:J70"/>
+    <mergeCell ref="B6:E6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D7:E7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
     <mergeCell ref="B71:C71"/>
     <mergeCell ref="D71:E71"/>
     <mergeCell ref="G71:H71"/>
@@ -14319,12 +14139,11 @@
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="I22:J22"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D7:E7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="B54:E54"/>
+    <mergeCell ref="B55:C55"/>
+    <mergeCell ref="D55:E55"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="G70:J70"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
